--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104700_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104700_W27.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1828</v>
+        <v>3.6808</v>
       </c>
       <c r="E2" t="n">
-        <v>3.314</v>
+        <v>4.0607</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1312</v>
+        <v>-0.38</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5854</v>
+        <v>3.5888</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2366</v>
+        <v>-1.2378</v>
       </c>
       <c r="I2" t="n">
-        <v>4.822</v>
+        <v>4.8266</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3574</v>
+        <v>4.3259</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6485</v>
       </c>
       <c r="L2" t="n">
-        <v>4.995</v>
+        <v>4.9744</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.772</v>
+        <v>-0.7371</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1731</v>
+        <v>-0.1478</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2172</v>
+        <v>-1.729</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.2652</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1738</v>
+        <v>-1.4639</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.87</v>
+        <v>2.0838</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5085</v>
+        <v>2.5786</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6385</v>
+        <v>-0.4948</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1211</v>
+        <v>1.1325</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2091</v>
+        <v>1.2173</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3682</v>
+        <v>1.3583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2471</v>
+        <v>-0.2257</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7489</v>
+        <v>-0.0487</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5939</v>
+        <v>0.6756</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.845</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1452</v>
+        <v>0.1738</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2168</v>
+        <v>2.5425</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0716</v>
+        <v>-2.3687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9859</v>
+        <v>0.1572</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3969</v>
+        <v>0.635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5891</v>
+        <v>-0.4777</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3135</v>
+        <v>1.4102</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0204</v>
+        <v>1.2098</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2931</v>
+        <v>0.2004</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6724</v>
+        <v>-1.253</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3764</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>-0.6781</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0711</v>
+        <v>-2.0729</v>
       </c>
       <c r="T4" t="n">
-        <v>0.738</v>
+        <v>-0.4533</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6669</v>
+        <v>-1.6196</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3856</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5536</v>
+        <v>-0.3804</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4083</v>
+        <v>-1.6275</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9619</v>
+        <v>1.2471</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9594</v>
+        <v>0.9805</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.469</v>
+        <v>0.3937</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4284</v>
+        <v>0.5868</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4997</v>
+        <v>0.2891</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1141</v>
+        <v>0.0065</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3856</v>
+        <v>0.2826</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5402</v>
+        <v>0.6914</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5831</v>
+        <v>0.3871</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0428</v>
+        <v>0.3043</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4865</v>
+        <v>-0.1544</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1179</v>
+        <v>0.3597</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3686</v>
+        <v>-0.5141</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4141</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.4445</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9923</v>
+        <v>0.1097</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5592</v>
+        <v>-0.5542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1516</v>
+        <v>-1.5795</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6393</v>
+        <v>-0.1864</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4877</v>
+        <v>-1.3931</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4382</v>
+        <v>-0.8423</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2224</v>
+        <v>0.403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2158</v>
+        <v>-1.2453</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2866</v>
+        <v>-0.7371</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5831</v>
+        <v>-0.5893</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7035</v>
+        <v>-0.1478</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.8112</v>
+        <v>-1.7756</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0434</v>
+        <v>-0.1375</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.7678</v>
+        <v>-1.6381</v>
       </c>
       <c r="V6" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6464</v>
+        <v>-0.6017</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0283</v>
+        <v>0.723</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6181</v>
+        <v>-1.3248</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5664</v>
+        <v>0.5468</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1803</v>
+        <v>-0.3508</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3861</v>
+        <v>0.8976</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7944</v>
+        <v>0.7581</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4187</v>
+        <v>-0.7379</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2131</v>
+        <v>1.496</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.772</v>
+        <v>-0.2113</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.599</v>
+        <v>0.3871</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1731</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9874</v>
+        <v>-0.5144</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3266</v>
+        <v>-0.0351</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6607</v>
+        <v>-0.4793</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.295</v>
+        <v>-0.8142</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0196</v>
+        <v>1.2668</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3145</v>
+        <v>-2.0811</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5535</v>
+        <v>1.9739</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.358</v>
+        <v>-0.4682</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9115</v>
+        <v>2.4421</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7848000000000001</v>
+        <v>2.4822</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7344000000000001</v>
+        <v>0.1067</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5192</v>
+        <v>2.3755</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2312</v>
+        <v>-0.5083</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3764</v>
+        <v>-0.5749</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6077</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2095</v>
+        <v>-1.7685</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.2349</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4443</v>
+        <v>-1.5336</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.719</v>
+        <v>-1.6156</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7691</v>
+        <v>-2.029</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4881</v>
+        <v>0.4134</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3894</v>
+        <v>-2.6038</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1759</v>
+        <v>-1.904</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7865</v>
+        <v>-0.6998</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4435</v>
+        <v>-2.3072</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4196</v>
+        <v>-2.2623</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8631</v>
+        <v>-0.0449</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8329</v>
+        <v>-0.2967</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7563</v>
+        <v>0.3583</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0767</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3958</v>
+        <v>-0.3077</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4597</v>
+        <v>0.1204</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8555</v>
+        <v>-0.4281</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7808</v>
+        <v>-1.8699</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4509</v>
+        <v>-2.2503</v>
       </c>
       <c r="F10" t="n">
-        <v>0.67</v>
+        <v>0.3804</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6066</v>
+        <v>-1.0107</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9003</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7063</v>
+        <v>-1.6564</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.285</v>
+        <v>-1.3442</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.245</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.04</v>
+        <v>-1.4303</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3216</v>
+        <v>0.3335</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3446</v>
+        <v>0.5595</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6663</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4691</v>
+        <v>-0.2462</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3266</v>
+        <v>0.232</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1425</v>
+        <v>-0.4782</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1455</v>
+        <v>-1.96</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3803</v>
+        <v>0.3376</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2348</v>
+        <v>-2.2976</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0218</v>
+        <v>-0.382</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6362</v>
+        <v>-1.1856</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6579</v>
+        <v>0.8037</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3369</v>
+        <v>1.4158</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0866</v>
+        <v>-0.4384</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4234</v>
+        <v>1.8542</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3151</v>
+        <v>-1.7977</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5496</v>
+        <v>-0.7472</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>-1.0505</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5093</v>
+        <v>-1.6479</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0907</v>
+        <v>0.06</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6001</v>
+        <v>-1.7078</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.799700000000001</v>
+        <v>-1.7479</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9355</v>
+        <v>5.7121</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.735100000000001</v>
+        <v>-7.460300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.772699999999999</v>
+        <v>2.8037</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4386</v>
+        <v>-2.4411</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2116</v>
+        <v>5.245</v>
       </c>
       <c r="J12" t="n">
-        <v>7.789</v>
+        <v>7.5459</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3259</v>
+        <v>-1.4303</v>
       </c>
       <c r="L12" t="n">
-        <v>9.115000000000002</v>
+        <v>8.976199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.0161</v>
+        <v>-4.742</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.113</v>
+        <v>-1.0109</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.9039</v>
+        <v>-3.731</v>
       </c>
       <c r="P12" t="n">
-        <v>4.536799999999999</v>
+        <v>4.5528</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.805099999999999</v>
+        <v>-6.829100000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.266</v>
+        <v>-10.2653</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7408000000000001</v>
+        <v>0.3217</v>
       </c>
       <c r="U12" t="n">
-        <v>-10.5252</v>
+        <v>-10.587</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
       <c r="W12" t="n">
-        <v>4.6921</v>
+        <v>4.6735</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5353</v>
+        <v>-3.5126</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0031</v>
+        <v>3.9169</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9182</v>
+        <v>3.99</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.0731</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2525</v>
+        <v>2.2345</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4445</v>
+        <v>2.436</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7632</v>
+        <v>3.7179</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2094</v>
+        <v>2.1923</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5538</v>
+        <v>1.5256</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5107</v>
+        <v>-1.4835</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7458</v>
+        <v>-1.7271</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1362</v>
+        <v>2.0694</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6747</v>
+        <v>1.7972</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4615</v>
+        <v>0.2722</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9623</v>
+        <v>3.1184</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6256</v>
+        <v>2.7292</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3367</v>
+        <v>0.3892</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4001</v>
+        <v>1.4042</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2913</v>
+        <v>0.3038</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1088</v>
+        <v>1.1005</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2899</v>
+        <v>1.272</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L14" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1102</v>
+        <v>0.1322</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7891</v>
+        <v>0.9418</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7894</v>
+        <v>0.9125</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0003</v>
+        <v>0.0294</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7592</v>
+        <v>1.8844</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8431999999999999</v>
+        <v>2.9605</v>
       </c>
       <c r="F15" t="n">
-        <v>0.916</v>
+        <v>-1.0761</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2755</v>
+        <v>0.8799</v>
       </c>
       <c r="H15" t="n">
-        <v>0.534</v>
+        <v>0.2096</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2585</v>
+        <v>0.6703</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1301</v>
+        <v>2.0387</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5817</v>
+        <v>0.2963</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7117</v>
+        <v>1.7425</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4055</v>
+        <v>-1.1588</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0477</v>
+        <v>-0.0866</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4532</v>
+        <v>-1.0722</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4572</v>
+        <v>1.0241</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4003</v>
+        <v>0.9217</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0569</v>
+        <v>0.1024</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7411</v>
+        <v>1.229</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0902</v>
+        <v>0.2362</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.349</v>
+        <v>0.9928</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8809</v>
+        <v>0.2758</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2092</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6717</v>
+        <v>-0.253</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0558</v>
+        <v>-0.1431</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3046</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7512</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1749</v>
+        <v>0.4189</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0954</v>
+        <v>-0.0433</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0795</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8868</v>
+        <v>0.9337</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0344</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1476</v>
+        <v>0.1187</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0929</v>
+        <v>1.0671</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7014</v>
+        <v>1.0713</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.0042</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2606</v>
+        <v>-0.7551</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0607</v>
+        <v>0.6201</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1999</v>
+        <v>-1.3751</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8556</v>
+        <v>0.1705</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.821</v>
+        <v>0.081</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1162</v>
+        <v>-0.9255</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0954</v>
+        <v>0.5306</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0209</v>
+        <v>-1.4562</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9395</v>
+        <v>1.1393</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8853</v>
+        <v>0.9008</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0541</v>
+        <v>0.2385</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.112</v>
+        <v>0.5849</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.723</v>
+        <v>0.065</v>
       </c>
       <c r="F18" t="n">
-        <v>0.611</v>
+        <v>0.5199</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1586</v>
+        <v>0.1572</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.14</v>
+        <v>-0.1407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1684</v>
+        <v>0.1352</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3432</v>
+        <v>-0.3555</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4906</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0098</v>
+        <v>0.022</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2131</v>
+        <v>-0.1927</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1585</v>
+        <v>0.8618</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2843</v>
+        <v>1.1167</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1258</v>
+        <v>-0.2549</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.512</v>
+        <v>0.1333</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3223</v>
+        <v>1.0023</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1898</v>
+        <v>-0.869</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-2.1848</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6146</v>
+        <v>0.1058</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3701</v>
+        <v>-2.2905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1979</v>
+        <v>-0.4956</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0968</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1011</v>
+        <v>-0.5301</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9534</v>
+        <v>-1.6891</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5178</v>
+        <v>0.0713</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4712</v>
+        <v>-1.7604</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.437</v>
+        <v>0.7733</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5202</v>
+        <v>0.4085</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0832</v>
+        <v>0.3648</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5736</v>
+        <v>-0.4209</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0322</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5414</v>
+        <v>-0.5069</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5249</v>
+        <v>-0.5219</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3359</v>
+        <v>-0.3351</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5622</v>
+        <v>-0.5592</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0487</v>
+        <v>0.101</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8622</v>
+        <v>-1.2818</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0876</v>
+        <v>-0.7197</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9498</v>
+        <v>-0.5621</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.172</v>
+        <v>-0.2486</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0965</v>
+        <v>-0.0522</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2685</v>
+        <v>-0.1965</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4667</v>
+        <v>0.8537</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5014</v>
+        <v>0.8192</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7053</v>
+        <v>-1.1023</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0619</v>
+        <v>-0.0866</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7672</v>
+        <v>-1.0157</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2365</v>
+        <v>1.5619</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5383</v>
+        <v>1.4769</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3018</v>
+        <v>0.0849</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0055</v>
+        <v>-2.3658</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4283</v>
+        <v>-2.3737</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4228</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4804</v>
+        <v>-0.4658</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5397</v>
+        <v>-0.4272</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0201</v>
+        <v>-0.0385</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6333</v>
+        <v>0.0425</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1314</v>
+        <v>-0.642</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7647</v>
+        <v>0.6845</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8471</v>
+        <v>-0.5083</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4082</v>
+        <v>0.2148</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2554</v>
+        <v>-0.723</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9947</v>
+        <v>0.8316</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1785</v>
+        <v>0.9983</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8163</v>
+        <v>-0.1667</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6362</v>
+        <v>-2.3701</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0834</v>
+        <v>-2.2196</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5528</v>
+        <v>-0.1505</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0904</v>
+        <v>-2.4826</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4876</v>
+        <v>0.5399</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3972</v>
+        <v>-3.0225</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2055</v>
+        <v>-1.6569</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.424</v>
+        <v>0.1239</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2185</v>
+        <v>-1.7808</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1151</v>
+        <v>-0.8257</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>0.416</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1787</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5054</v>
+        <v>0.6377</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1221</v>
+        <v>0.4177</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6167</v>
+        <v>0.22</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7317</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0575</v>
+        <v>-2.702</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0345</v>
+        <v>-0.457</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0231</v>
+        <v>-2.245</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4565</v>
+        <v>-1.0966</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4139</v>
+        <v>-1.4959</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0426</v>
+        <v>0.3993</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0837</v>
+        <v>-1.2301</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6172</v>
+        <v>-1.4381</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7009</v>
+        <v>0.2081</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5402</v>
+        <v>0.1335</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2033</v>
+        <v>-0.0578</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7435</v>
+        <v>0.1912</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.121</v>
+        <v>0.4354</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2843</v>
+        <v>0.7731</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1633</v>
+        <v>-0.3377</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.799599999999999</v>
+        <v>2.793399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>6.642500000000002</v>
+        <v>6.370500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8428</v>
+        <v>-3.577100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.772700000000001</v>
+        <v>-2.803800000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4385</v>
+        <v>2.4411</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.211399999999999</v>
+        <v>-5.2447</v>
       </c>
       <c r="J25" t="n">
-        <v>5.0162</v>
+        <v>4.742</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1126</v>
+        <v>1.010800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.9036</v>
+        <v>3.7312</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.789000000000001</v>
+        <v>-7.545800000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3258</v>
+        <v>1.4304</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.115100000000002</v>
+        <v>-8.976099999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R25" t="n">
-        <v>6.805099999999999</v>
+        <v>6.8291</v>
       </c>
       <c r="S25" t="n">
-        <v>11.2662</v>
+        <v>11.311</v>
       </c>
       <c r="T25" t="n">
-        <v>10.5252</v>
+        <v>10.5871</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7410000000000001</v>
+        <v>0.7239000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="W25" t="n">
-        <v>2.4427</v>
+        <v>2.4231</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.5995</v>
+        <v>-3.584</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104700_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104700_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-3.5126</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104700_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-3.584</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
